--- a/exports/trend_1d/HINDALCO_full_report.xlsx
+++ b/exports/trend_1d/HINDALCO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.35</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42068</v>
+        <v>42072</v>
       </c>
       <c r="H2" t="n">
-        <v>148.1</v>
+        <v>140.8</v>
       </c>
       <c r="I2" t="n">
         <v>142.3919020570348</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K2" t="n">
-        <v>4.37</v>
+        <v>-0.78</v>
       </c>
       <c r="L2" t="n">
         <v>2.92</v>
@@ -555,7 +578,7 @@
         <v>3.38</v>
       </c>
       <c r="N2" t="n">
-        <v>3.52</v>
+        <v>4.93</v>
       </c>
       <c r="O2" t="n">
         <v>-0.18</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>15.66</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42132</v>
+        <v>42135</v>
       </c>
       <c r="H3" t="n">
-        <v>138.94</v>
+        <v>142.5</v>
       </c>
       <c r="I3" t="n">
         <v>140.8914874280931</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K3" t="n">
-        <v>1.32</v>
+        <v>-1.21</v>
       </c>
       <c r="L3" t="n">
         <v>6.43</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>10.33</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42156</v>
+        <v>42157</v>
       </c>
       <c r="H4" t="n">
-        <v>128.35</v>
+        <v>123.25</v>
       </c>
       <c r="I4" t="n">
         <v>127.7747428047267</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>-9.93</v>
+        <v>-13.51</v>
       </c>
       <c r="L4" t="n">
-        <v>10.35</v>
+        <v>13.75</v>
       </c>
       <c r="M4" t="n">
         <v>1.96</v>
       </c>
       <c r="N4" t="n">
-        <v>3.44</v>
+        <v>3.97</v>
       </c>
       <c r="O4" t="n">
         <v>2.56</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.36</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42283</v>
+        <v>42284</v>
       </c>
       <c r="H5" t="n">
-        <v>75</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>79.39540956611323</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K5" t="n">
-        <v>39.15</v>
+        <v>33.55</v>
       </c>
       <c r="L5" t="n">
         <v>4.82</v>
@@ -726,7 +785,7 @@
         <v>3.37</v>
       </c>
       <c r="N5" t="n">
-        <v>8.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>-3.97</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>17.72</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42328</v>
+        <v>42331</v>
       </c>
       <c r="H6" t="n">
-        <v>77.2</v>
+        <v>74.25</v>
       </c>
       <c r="I6" t="n">
         <v>75.74772666076792</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.74</v>
+        <v>-9.34</v>
       </c>
       <c r="L6" t="n">
-        <v>9.16</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M6" t="n">
         <v>8.630000000000001</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>15.05</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42360</v>
+        <v>42361</v>
       </c>
       <c r="H7" t="n">
-        <v>79.59</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>82.50774404401214</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.19</v>
+        <v>-13</v>
       </c>
       <c r="L7" t="n">
-        <v>10.44</v>
+        <v>13.4</v>
       </c>
       <c r="M7" t="n">
         <v>1.29</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>5.42</v>
       </c>
       <c r="O7" t="n">
         <v>-3.82</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>11.9</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H8" t="n">
-        <v>80.55</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>77.8713494565349</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.99</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>5.01</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.82</v>
+        <v>1.92</v>
       </c>
       <c r="N8" t="n">
         <v>4.89</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>12.7</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42430</v>
+        <v>42431</v>
       </c>
       <c r="H9" t="n">
-        <v>70.25</v>
+        <v>74.95</v>
       </c>
       <c r="I9" t="n">
         <v>72.78365677672909</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K9" t="n">
-        <v>8.35</v>
+        <v>2.22</v>
       </c>
       <c r="L9" t="n">
         <v>3.59</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>15.92</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42494</v>
+        <v>42495</v>
       </c>
       <c r="H10" t="n">
-        <v>91.15000000000001</v>
+        <v>90.45</v>
       </c>
       <c r="I10" t="n">
         <v>90.68130551975156</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K10" t="n">
-        <v>21.61</v>
+        <v>20.68</v>
       </c>
       <c r="L10" t="n">
         <v>4.87</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>15.98</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42517</v>
+        <v>42520</v>
       </c>
       <c r="H11" t="n">
-        <v>91.90000000000001</v>
+        <v>102.95</v>
       </c>
       <c r="I11" t="n">
         <v>95.73175114193816</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6</v>
+        <v>-13.82</v>
       </c>
       <c r="L11" t="n">
-        <v>3.81</v>
+        <v>14.43</v>
       </c>
       <c r="M11" t="n">
-        <v>3.13</v>
+        <v>8.81</v>
       </c>
       <c r="N11" t="n">
-        <v>2.84</v>
+        <v>12.02</v>
       </c>
       <c r="O11" t="n">
         <v>-0.77</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>13.96</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42622</v>
+        <v>42625</v>
       </c>
       <c r="H12" t="n">
-        <v>154.85</v>
+        <v>140.85</v>
       </c>
       <c r="I12" t="n">
         <v>148.8620003796003</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K12" t="n">
-        <v>50.41</v>
+        <v>36.81</v>
       </c>
       <c r="L12" t="n">
         <v>4.66</v>
@@ -1125,7 +1268,7 @@
         <v>4.48</v>
       </c>
       <c r="N12" t="n">
-        <v>5.33</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>12.02</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>15.4</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42648</v>
+        <v>42649</v>
       </c>
       <c r="H13" t="n">
-        <v>157.25</v>
+        <v>158.35</v>
       </c>
       <c r="I13" t="n">
         <v>158.2341767232713</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K13" t="n">
-        <v>-11.64</v>
+        <v>-12.42</v>
       </c>
       <c r="L13" t="n">
-        <v>13.1</v>
+        <v>14.8</v>
       </c>
       <c r="M13" t="n">
         <v>2.57</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.48</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42725</v>
+        <v>42726</v>
       </c>
       <c r="H14" t="n">
-        <v>168.8</v>
+        <v>161.25</v>
       </c>
       <c r="I14" t="n">
         <v>161.9169538722029</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K14" t="n">
-        <v>6.6</v>
+        <v>1.83</v>
       </c>
       <c r="L14" t="n">
         <v>6.92</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>13.05</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H15" t="n">
-        <v>164.4</v>
+        <v>174.95</v>
       </c>
       <c r="I15" t="n">
         <v>171.2229998187642</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.95</v>
+        <v>-8.5</v>
       </c>
       <c r="L15" t="n">
-        <v>4.62</v>
+        <v>8.93</v>
       </c>
       <c r="M15" t="n">
-        <v>0.73</v>
+        <v>1.64</v>
       </c>
       <c r="N15" t="n">
-        <v>4.05</v>
+        <v>6.42</v>
       </c>
       <c r="O15" t="n">
         <v>-4.47</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>12.23</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H16" t="n">
-        <v>230.9</v>
+        <v>229.1</v>
       </c>
       <c r="I16" t="n">
         <v>230.2839022337735</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="K16" t="n">
-        <v>31.98</v>
+        <v>30.95</v>
       </c>
       <c r="L16" t="n">
         <v>4.86</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>174</v>
+        <v>175</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>9</v>
+      </c>
+      <c r="U16" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>9.92</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43017</v>
+        <v>43018</v>
       </c>
       <c r="H17" t="n">
-        <v>249.5</v>
+        <v>252.05</v>
       </c>
       <c r="I17" t="n">
         <v>251.8163808807633</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.9</v>
+        <v>-10.02</v>
       </c>
       <c r="L17" t="n">
-        <v>10.61</v>
+        <v>10.65</v>
       </c>
       <c r="M17" t="n">
         <v>1.2</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.32</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43053</v>
+        <v>43054</v>
       </c>
       <c r="H18" t="n">
-        <v>261</v>
+        <v>251.85</v>
       </c>
       <c r="I18" t="n">
         <v>254.0829531082471</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K18" t="n">
-        <v>3.55</v>
+        <v>-0.08</v>
       </c>
       <c r="L18" t="n">
         <v>2.16</v>
@@ -1467,7 +1682,7 @@
         <v>0.85</v>
       </c>
       <c r="N18" t="n">
-        <v>2.22</v>
+        <v>3.51</v>
       </c>
       <c r="O18" t="n">
         <v>1.02</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>11.29</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43088</v>
+        <v>43089</v>
       </c>
       <c r="H19" t="n">
-        <v>254.3</v>
+        <v>258.35</v>
       </c>
       <c r="I19" t="n">
         <v>255.8086021686662</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.97</v>
+        <v>-2.58</v>
       </c>
       <c r="L19" t="n">
         <v>5.26</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>10.13</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43117</v>
+        <v>43118</v>
       </c>
       <c r="H20" t="n">
-        <v>262.75</v>
+        <v>253.9</v>
       </c>
       <c r="I20" t="n">
         <v>257.1099504037845</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7</v>
+        <v>-1.72</v>
       </c>
       <c r="L20" t="n">
         <v>2.77</v>
@@ -1581,7 +1820,7 @@
         <v>0.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.31</v>
+        <v>3.37</v>
       </c>
       <c r="O20" t="n">
         <v>1.59</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>10.83</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43199</v>
+        <v>43200</v>
       </c>
       <c r="H21" t="n">
-        <v>221.35</v>
+        <v>230</v>
       </c>
       <c r="I21" t="n">
         <v>229.78619413122</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K21" t="n">
-        <v>12.82</v>
+        <v>9.41</v>
       </c>
       <c r="L21" t="n">
         <v>6.62</v>
       </c>
       <c r="M21" t="n">
-        <v>2.94</v>
+        <v>3.91</v>
       </c>
       <c r="N21" t="n">
         <v>6.65</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>11.35</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43220</v>
+        <v>43222</v>
       </c>
       <c r="H22" t="n">
-        <v>235.65</v>
+        <v>228.05</v>
       </c>
       <c r="I22" t="n">
         <v>230.1676610147178</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K22" t="n">
-        <v>2.46</v>
+        <v>-0.85</v>
       </c>
       <c r="L22" t="n">
-        <v>0.65</v>
+        <v>1.65</v>
       </c>
       <c r="M22" t="n">
         <v>6.49</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>13.71</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43320</v>
+        <v>43321</v>
       </c>
       <c r="H23" t="n">
-        <v>220.6</v>
+        <v>227.45</v>
       </c>
       <c r="I23" t="n">
         <v>222.8223320979271</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K23" t="n">
-        <v>3.27</v>
+        <v>0.26</v>
       </c>
       <c r="L23" t="n">
         <v>12.04</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>11.76</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43383</v>
+        <v>43384</v>
       </c>
       <c r="H24" t="n">
-        <v>226.9</v>
+        <v>216.5</v>
       </c>
       <c r="I24" t="n">
         <v>219.9579021813182</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.24</v>
+        <v>-4.81</v>
       </c>
       <c r="L24" t="n">
         <v>7.36</v>
       </c>
       <c r="M24" t="n">
-        <v>2.51</v>
+        <v>4.41</v>
       </c>
       <c r="N24" t="n">
         <v>7.67</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>17.6</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43543</v>
+        <v>43544</v>
       </c>
       <c r="H25" t="n">
-        <v>202.35</v>
+        <v>207.15</v>
       </c>
       <c r="I25" t="n">
         <v>205.7910534260251</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K25" t="n">
-        <v>6.54</v>
+        <v>4.32</v>
       </c>
       <c r="L25" t="n">
         <v>13.3</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>8.32</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43579</v>
+        <v>43580</v>
       </c>
       <c r="H26" t="n">
-        <v>200.7</v>
+        <v>196.55</v>
       </c>
       <c r="I26" t="n">
         <v>198.9774522072112</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.11</v>
+        <v>-5.12</v>
       </c>
       <c r="L26" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="M26" t="n">
         <v>1.24</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>10.36</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43641</v>
+        <v>43642</v>
       </c>
       <c r="H27" t="n">
-        <v>202.5</v>
+        <v>208.35</v>
       </c>
       <c r="I27" t="n">
         <v>207.9075285492297</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.03</v>
+        <v>-6</v>
       </c>
       <c r="L27" t="n">
-        <v>5.65</v>
+        <v>6.31</v>
       </c>
       <c r="M27" t="n">
         <v>1.52</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>10.57</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43675</v>
+        <v>43676</v>
       </c>
       <c r="H28" t="n">
-        <v>193.25</v>
+        <v>190.1</v>
       </c>
       <c r="I28" t="n">
         <v>192.1482932940792</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.25</v>
+        <v>-8.76</v>
       </c>
       <c r="L28" t="n">
-        <v>7.66</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="M28" t="n">
         <v>0.96</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>10.23</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43719</v>
+        <v>43720</v>
       </c>
       <c r="H29" t="n">
-        <v>193.45</v>
+        <v>197.1</v>
       </c>
       <c r="I29" t="n">
         <v>194.6951215916887</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.76</v>
+        <v>-3.68</v>
       </c>
       <c r="L29" t="n">
-        <v>2.47</v>
+        <v>3.95</v>
       </c>
       <c r="M29" t="n">
         <v>1.42</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.42</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43761</v>
+        <v>43762</v>
       </c>
       <c r="H30" t="n">
-        <v>185.1</v>
+        <v>181.35</v>
       </c>
       <c r="I30" t="n">
         <v>181.943304472478</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K30" t="n">
-        <v>-6.09</v>
+        <v>-7.99</v>
       </c>
       <c r="L30" t="n">
         <v>8.68</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.39</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43773</v>
+        <v>43774</v>
       </c>
       <c r="H31" t="n">
-        <v>197.95</v>
+        <v>198.6</v>
       </c>
       <c r="I31" t="n">
         <v>198.0832332241326</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K31" t="n">
-        <v>-9.15</v>
+        <v>-9.51</v>
       </c>
       <c r="L31" t="n">
         <v>12.54</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.15</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43854</v>
+        <v>43857</v>
       </c>
       <c r="H32" t="n">
-        <v>205.4</v>
+        <v>198.25</v>
       </c>
       <c r="I32" t="n">
         <v>203.0664645755926</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K32" t="n">
-        <v>3.42</v>
+        <v>-0.18</v>
       </c>
       <c r="L32" t="n">
         <v>5.82</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>8.56</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43936</v>
+        <v>43937</v>
       </c>
       <c r="H33" t="n">
-        <v>115.1</v>
+        <v>120.55</v>
       </c>
       <c r="I33" t="n">
         <v>118.0450063960776</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K33" t="n">
-        <v>41.94</v>
+        <v>39.19</v>
       </c>
       <c r="L33" t="n">
         <v>2.67</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>26.12</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44083</v>
+        <v>44084</v>
       </c>
       <c r="H34" t="n">
-        <v>182.8</v>
+        <v>176.65</v>
       </c>
       <c r="I34" t="n">
         <v>178.5079354826634</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K34" t="n">
-        <v>51.64</v>
+        <v>46.54</v>
       </c>
       <c r="L34" t="n">
         <v>14.77</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>14.65</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44124</v>
+        <v>44125</v>
       </c>
       <c r="H35" t="n">
-        <v>180.8</v>
+        <v>185.95</v>
       </c>
       <c r="I35" t="n">
         <v>183.2441706000466</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.35</v>
+        <v>-5.26</v>
       </c>
       <c r="L35" t="n">
-        <v>4.9</v>
+        <v>6.14</v>
       </c>
       <c r="M35" t="n">
         <v>2.35</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>11.61</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44217</v>
+        <v>44218</v>
       </c>
       <c r="H36" t="n">
-        <v>248.9</v>
+        <v>239.2</v>
       </c>
       <c r="I36" t="n">
         <v>240.1636158135903</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K36" t="n">
-        <v>33.85</v>
+        <v>28.64</v>
       </c>
       <c r="L36" t="n">
         <v>11.11</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>13.92</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44230</v>
+        <v>44231</v>
       </c>
       <c r="H37" t="n">
-        <v>257.25</v>
+        <v>261.85</v>
       </c>
       <c r="I37" t="n">
         <v>257.6847710250144</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.55</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>10.12</v>
+        <v>11.79</v>
       </c>
       <c r="M37" t="n">
         <v>1.26</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>12.08</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H38" t="n">
-        <v>317.75</v>
+        <v>314</v>
       </c>
       <c r="I38" t="n">
         <v>315.0606598075611</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K38" t="n">
-        <v>21.35</v>
+        <v>19.92</v>
       </c>
       <c r="L38" t="n">
         <v>2.27</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>12.47</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44293</v>
+        <v>44294</v>
       </c>
       <c r="H39" t="n">
-        <v>352.2</v>
+        <v>365.2</v>
       </c>
       <c r="I39" t="n">
         <v>353.1493523936491</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K39" t="n">
-        <v>-12.17</v>
+        <v>-16.31</v>
       </c>
       <c r="L39" t="n">
-        <v>14.87</v>
+        <v>19.11</v>
       </c>
       <c r="M39" t="n">
         <v>1.31</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>12.22</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44426</v>
+        <v>44428</v>
       </c>
       <c r="H40" t="n">
-        <v>426.95</v>
+        <v>403.65</v>
       </c>
       <c r="I40" t="n">
         <v>403.9645695335996</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K40" t="n">
-        <v>16.91</v>
+        <v>10.53</v>
       </c>
       <c r="L40" t="n">
         <v>9.199999999999999</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>12.83</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44438</v>
+        <v>44439</v>
       </c>
       <c r="H41" t="n">
-        <v>448.05</v>
+        <v>468.3</v>
       </c>
       <c r="I41" t="n">
         <v>454.7046504312592</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K41" t="n">
-        <v>-11</v>
+        <v>-16.02</v>
       </c>
       <c r="L41" t="n">
-        <v>12.1</v>
+        <v>16.72</v>
       </c>
       <c r="M41" t="n">
         <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>3.44</v>
+        <v>4.52</v>
       </c>
       <c r="O41" t="n">
         <v>-5.46</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>12.62</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44490</v>
+        <v>44491</v>
       </c>
       <c r="H42" t="n">
-        <v>493.75</v>
+        <v>470.45</v>
       </c>
       <c r="I42" t="n">
         <v>483.9655453300426</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K42" t="n">
-        <v>5.43</v>
+        <v>0.46</v>
       </c>
       <c r="L42" t="n">
         <v>6.3</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>15.11</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44560</v>
+        <v>44561</v>
       </c>
       <c r="H43" t="n">
-        <v>449.65</v>
+        <v>475.55</v>
       </c>
       <c r="I43" t="n">
         <v>474.8806774157202</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K43" t="n">
-        <v>4.42</v>
+        <v>-1.08</v>
       </c>
       <c r="L43" t="n">
         <v>4.58</v>
@@ -2892,7 +3407,7 @@
         <v>1.64</v>
       </c>
       <c r="N43" t="n">
-        <v>5.02</v>
+        <v>5.76</v>
       </c>
       <c r="O43" t="n">
         <v>-4.72</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.51</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44650</v>
+        <v>44651</v>
       </c>
       <c r="H44" t="n">
-        <v>599.8</v>
+        <v>569.5</v>
       </c>
       <c r="I44" t="n">
         <v>572.595245728446</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K44" t="n">
-        <v>26.13</v>
+        <v>19.76</v>
       </c>
       <c r="L44" t="n">
         <v>4.22</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>14.02</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44762</v>
+        <v>44763</v>
       </c>
       <c r="H45" t="n">
-        <v>369.35</v>
+        <v>375.95</v>
       </c>
       <c r="I45" t="n">
         <v>372.8557009880678</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K45" t="n">
-        <v>35.14</v>
+        <v>33.99</v>
       </c>
       <c r="L45" t="n">
         <v>5.41</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.59</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H46" t="n">
-        <v>412.1</v>
+        <v>396.35</v>
       </c>
       <c r="I46" t="n">
         <v>401.8827799146953</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K46" t="n">
-        <v>9.619999999999999</v>
+        <v>5.43</v>
       </c>
       <c r="L46" t="n">
         <v>1.36</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>12.52</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44838</v>
+        <v>44840</v>
       </c>
       <c r="H47" t="n">
-        <v>394.05</v>
+        <v>412.65</v>
       </c>
       <c r="I47" t="n">
         <v>411.2966304212453</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K47" t="n">
-        <v>0.58</v>
+        <v>-4.11</v>
       </c>
       <c r="L47" t="n">
-        <v>4.13</v>
+        <v>4.44</v>
       </c>
       <c r="M47" t="n">
         <v>3.95</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>13.49</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H48" t="n">
-        <v>455.5</v>
+        <v>429.55</v>
       </c>
       <c r="I48" t="n">
         <v>434.804282082556</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K48" t="n">
-        <v>10.38</v>
+        <v>4.1</v>
       </c>
       <c r="L48" t="n">
         <v>7.89</v>
@@ -3177,7 +3752,7 @@
         <v>1.87</v>
       </c>
       <c r="N48" t="n">
-        <v>4.66</v>
+        <v>5.7</v>
       </c>
       <c r="O48" t="n">
         <v>4.72</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>12.33</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44925</v>
+        <v>44928</v>
       </c>
       <c r="H49" t="n">
-        <v>473.35</v>
+        <v>487.05</v>
       </c>
       <c r="I49" t="n">
         <v>480.1883164723137</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K49" t="n">
-        <v>-10.2</v>
+        <v>-13.39</v>
       </c>
       <c r="L49" t="n">
-        <v>12.28</v>
+        <v>14.31</v>
       </c>
       <c r="M49" t="n">
         <v>1.13</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>10.27</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44960</v>
+        <v>44963</v>
       </c>
       <c r="H50" t="n">
-        <v>459.65</v>
+        <v>447.35</v>
       </c>
       <c r="I50" t="n">
         <v>457.4871626463931</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.63</v>
+        <v>-8.15</v>
       </c>
       <c r="L50" t="n">
-        <v>7.57</v>
+        <v>8.43</v>
       </c>
       <c r="M50" t="n">
         <v>1.95</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>11.14</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45029</v>
+        <v>45033</v>
       </c>
       <c r="H51" t="n">
-        <v>422.05</v>
+        <v>428.7</v>
       </c>
       <c r="I51" t="n">
         <v>426.0080772724893</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K51" t="n">
-        <v>5.66</v>
+        <v>4.17</v>
       </c>
       <c r="L51" t="n">
         <v>2.16</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>7.44</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45057</v>
+        <v>45058</v>
       </c>
       <c r="H52" t="n">
-        <v>420.85</v>
+        <v>404.75</v>
       </c>
       <c r="I52" t="n">
         <v>416.6551323224731</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.83</v>
+        <v>-5.59</v>
       </c>
       <c r="L52" t="n">
-        <v>2.41</v>
+        <v>5.81</v>
       </c>
       <c r="M52" t="n">
         <v>1.15</v>
       </c>
       <c r="N52" t="n">
-        <v>3.57</v>
+        <v>3.83</v>
       </c>
       <c r="O52" t="n">
         <v>1.58</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>9.73</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45096</v>
+        <v>45097</v>
       </c>
       <c r="H53" t="n">
-        <v>426.15</v>
+        <v>428.95</v>
       </c>
       <c r="I53" t="n">
         <v>428.402333861796</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.29</v>
+        <v>-5.98</v>
       </c>
       <c r="L53" t="n">
-        <v>6.73</v>
+        <v>7.04</v>
       </c>
       <c r="M53" t="n">
         <v>1.4</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.22</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H54" t="n">
-        <v>471.75</v>
+        <v>456.7</v>
       </c>
       <c r="I54" t="n">
         <v>462.317061747664</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K54" t="n">
-        <v>9.98</v>
+        <v>6.47</v>
       </c>
       <c r="L54" t="n">
         <v>5.01</v>
@@ -3519,7 +4166,7 @@
         <v>1.94</v>
       </c>
       <c r="N54" t="n">
-        <v>2.75</v>
+        <v>3.19</v>
       </c>
       <c r="O54" t="n">
         <v>0.66</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>9.77</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45243</v>
+        <v>45245</v>
       </c>
       <c r="H55" t="n">
-        <v>487.5</v>
+        <v>505.4</v>
       </c>
       <c r="I55" t="n">
         <v>491.5781101748853</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.74</v>
+        <v>-10.66</v>
       </c>
       <c r="L55" t="n">
-        <v>7.81</v>
+        <v>12.44</v>
       </c>
       <c r="M55" t="n">
         <v>2.04</v>
       </c>
       <c r="N55" t="n">
-        <v>2.49</v>
+        <v>3.67</v>
       </c>
       <c r="O55" t="n">
         <v>-3.19</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>7.31</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45307</v>
+        <v>45308</v>
       </c>
       <c r="H56" t="n">
-        <v>579.55</v>
+        <v>560.25</v>
       </c>
       <c r="I56" t="n">
         <v>571.4765330342059</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K56" t="n">
-        <v>14.67</v>
+        <v>10.85</v>
       </c>
       <c r="L56" t="n">
         <v>2.72</v>
       </c>
       <c r="M56" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="N56" t="n">
         <v>3.88</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.65</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45329</v>
+        <v>45330</v>
       </c>
       <c r="H57" t="n">
-        <v>592.25</v>
+        <v>601.3</v>
       </c>
       <c r="I57" t="n">
         <v>592.5413554897527</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.71</v>
+        <v>-7.33</v>
       </c>
       <c r="L57" t="n">
-        <v>7.48</v>
+        <v>8.69</v>
       </c>
       <c r="M57" t="n">
         <v>1.59</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45334</v>
+        <v>45335</v>
       </c>
       <c r="H58" t="n">
-        <v>582.45</v>
+        <v>510.1</v>
       </c>
       <c r="I58" t="n">
         <v>550.9212355108252</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.13</v>
+        <v>-15.17</v>
       </c>
       <c r="L58" t="n">
-        <v>4.16</v>
+        <v>17.45</v>
       </c>
       <c r="M58" t="n">
-        <v>0.05</v>
+        <v>7.46</v>
       </c>
       <c r="N58" t="n">
-        <v>1.66</v>
+        <v>12.42</v>
       </c>
       <c r="O58" t="n">
         <v>1.53</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>15.82</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45373</v>
+        <v>45377</v>
       </c>
       <c r="H59" t="n">
-        <v>547.75</v>
+        <v>558.65</v>
       </c>
       <c r="I59" t="n">
         <v>548.897838340251</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K59" t="n">
-        <v>-7.38</v>
+        <v>-9.52</v>
       </c>
       <c r="L59" t="n">
-        <v>7.95</v>
+        <v>9.98</v>
       </c>
       <c r="M59" t="n">
         <v>4.57</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45495</v>
+        <v>45496</v>
       </c>
       <c r="H60" t="n">
-        <v>672.3</v>
+        <v>653.5</v>
       </c>
       <c r="I60" t="n">
         <v>653.821213057162</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K60" t="n">
-        <v>20.34</v>
+        <v>16.98</v>
       </c>
       <c r="L60" t="n">
         <v>2.44</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45524</v>
+        <v>45525</v>
       </c>
       <c r="H61" t="n">
-        <v>672.9</v>
+        <v>685.6</v>
       </c>
       <c r="I61" t="n">
         <v>679.4822966546166</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.97</v>
+        <v>-4.91</v>
       </c>
       <c r="L61" t="n">
-        <v>5.72</v>
+        <v>6.6</v>
       </c>
       <c r="M61" t="n">
         <v>2.41</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>9.5</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H62" t="n">
-        <v>659.5</v>
+        <v>647.7</v>
       </c>
       <c r="I62" t="n">
         <v>650.4815845939696</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.81</v>
+        <v>-5.53</v>
       </c>
       <c r="L62" t="n">
-        <v>5.05</v>
+        <v>5.86</v>
       </c>
       <c r="M62" t="n">
         <v>1.8</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>7.9</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45558</v>
+        <v>45559</v>
       </c>
       <c r="H63" t="n">
-        <v>690.55</v>
+        <v>717.85</v>
       </c>
       <c r="I63" t="n">
         <v>698.870458724246</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K63" t="n">
-        <v>-6.62</v>
+        <v>-10.83</v>
       </c>
       <c r="L63" t="n">
-        <v>7.89</v>
+        <v>11.12</v>
       </c>
       <c r="M63" t="n">
         <v>1.59</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>8.76</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45588</v>
+        <v>45589</v>
       </c>
       <c r="H64" t="n">
-        <v>717.1</v>
+        <v>690.7</v>
       </c>
       <c r="I64" t="n">
         <v>702.29118668273</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.1</v>
+        <v>-3.78</v>
       </c>
       <c r="L64" t="n">
-        <v>3.46</v>
+        <v>7.12</v>
       </c>
       <c r="M64" t="n">
         <v>1.63</v>
       </c>
       <c r="N64" t="n">
-        <v>2.62</v>
+        <v>3.68</v>
       </c>
       <c r="O64" t="n">
         <v>3.95</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>10.66</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="H65" t="n">
-        <v>602.6</v>
+        <v>617</v>
       </c>
       <c r="I65" t="n">
         <v>612.9116727280798</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K65" t="n">
-        <v>12.76</v>
+        <v>10.67</v>
       </c>
       <c r="L65" t="n">
         <v>3.52</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>8.59</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45684</v>
+        <v>45685</v>
       </c>
       <c r="H66" t="n">
-        <v>586.9</v>
+        <v>573.85</v>
       </c>
       <c r="I66" t="n">
         <v>575.4520398087166</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K66" t="n">
-        <v>-4.88</v>
+        <v>-6.99</v>
       </c>
       <c r="L66" t="n">
-        <v>5.13</v>
+        <v>7.89</v>
       </c>
       <c r="M66" t="n">
         <v>1.13</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>9.32</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="H67" t="n">
-        <v>611.45</v>
+        <v>626.3</v>
       </c>
       <c r="I67" t="n">
         <v>617.8847052530587</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K67" t="n">
-        <v>-6.55</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>7.35</v>
+        <v>9.5</v>
       </c>
       <c r="M67" t="n">
         <v>1.12</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>10.05</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H68" t="n">
-        <v>652.65</v>
+        <v>599.95</v>
       </c>
       <c r="I68" t="n">
         <v>649.8346766993363</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K68" t="n">
-        <v>4.21</v>
+        <v>-4.21</v>
       </c>
       <c r="L68" t="n">
-        <v>3.15</v>
+        <v>4.75</v>
       </c>
       <c r="M68" t="n">
         <v>1.77</v>
       </c>
       <c r="N68" t="n">
-        <v>3.5</v>
+        <v>8.07</v>
       </c>
       <c r="O68" t="n">
         <v>2.43</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>13.76</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45777</v>
+        <v>45779</v>
       </c>
       <c r="H69" t="n">
-        <v>624.65</v>
+        <v>632.1</v>
       </c>
       <c r="I69" t="n">
         <v>629.8115818947026</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K69" t="n">
-        <v>-4.12</v>
+        <v>-5.36</v>
       </c>
       <c r="L69" t="n">
-        <v>7.51</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M69" t="n">
         <v>3.72</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>8.32</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="H70" t="n">
-        <v>831.4</v>
+        <v>788.4</v>
       </c>
       <c r="I70" t="n">
         <v>805.575215261829</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K70" t="n">
-        <v>31.53</v>
+        <v>24.73</v>
       </c>
       <c r="L70" t="n">
         <v>4.49</v>
       </c>
       <c r="M70" t="n">
-        <v>2.47</v>
+        <v>5.22</v>
       </c>
       <c r="N70" t="n">
-        <v>2.64</v>
+        <v>5.17</v>
       </c>
       <c r="O70" t="n">
         <v>1.19</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>7</v>
+      </c>
+      <c r="U70" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>7.25</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="H71" t="n">
-        <v>824.35</v>
+        <v>852.1</v>
       </c>
       <c r="I71" t="n">
         <v>832.9968029061063</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K71" t="n">
-        <v>-4.56</v>
+        <v>-8.08</v>
       </c>
       <c r="L71" t="n">
-        <v>5.72</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M71" t="n">
         <v>1.18</v>
       </c>
       <c r="N71" t="n">
-        <v>2.21</v>
+        <v>3.37</v>
       </c>
       <c r="O71" t="n">
         <v>-5.17</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,25 +5387,25 @@
         <v>7.24</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="H72" t="n">
-        <v>962.6</v>
+        <v>908.2</v>
       </c>
       <c r="I72" t="n">
         <v>942.056423977727</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K72" t="n">
-        <v>12.97</v>
+        <v>6.58</v>
       </c>
       <c r="L72" t="n">
         <v>2.52</v>
       </c>
       <c r="M72" t="n">
-        <v>2.35</v>
+        <v>4.43</v>
       </c>
       <c r="N72" t="n">
         <v>6</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>11.35</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="H73" t="n">
-        <v>927.45</v>
+        <v>954.5</v>
       </c>
       <c r="I73" t="n">
         <v>950.2820590507858</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K73" t="n">
-        <v>-2.12</v>
+        <v>-5.1</v>
       </c>
       <c r="L73" t="n">
         <v>8.289999999999999</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>10.77</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H74" t="n">
-        <v>1076.7</v>
+        <v>1039.3</v>
       </c>
       <c r="I74" t="n">
         <v>1052.949589011804</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K74" t="n">
-        <v>12.8</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="L74" t="n">
         <v>2.26</v>
@@ -4659,7 +5546,7 @@
         <v>2.89</v>
       </c>
       <c r="N74" t="n">
-        <v>3.24</v>
+        <v>3.47</v>
       </c>
       <c r="O74" t="n">
         <v>2.92</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>10.72</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="H75" t="n">
-        <v>994.9</v>
+        <v>1020</v>
       </c>
       <c r="I75" t="n">
         <v>996.5872467921558</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K75" t="n">
-        <v>4.27</v>
+        <v>1.86</v>
       </c>
       <c r="L75" t="n">
         <v>2.66</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>7.07</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="H76" t="n">
-        <v>1014</v>
+        <v>981.5</v>
       </c>
       <c r="I76" t="n">
         <v>997.5721562908298</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.59</v>
+        <v>-3.77</v>
       </c>
       <c r="L76" t="n">
-        <v>2.64</v>
+        <v>4.6</v>
       </c>
       <c r="M76" t="n">
-        <v>1.06</v>
+        <v>2.37</v>
       </c>
       <c r="N76" t="n">
-        <v>2.99</v>
+        <v>3.21</v>
       </c>
       <c r="O76" t="n">
         <v>2.52</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4833,6 +5756,14 @@
       <c r="Q77" t="n">
         <v>31</v>
       </c>
+      <c r="R77" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9791,7 +10722,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.3</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="6">
@@ -9801,7 +10732,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -9811,7 +10742,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8">
@@ -9821,7 +10752,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -9831,7 +10762,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="10">
@@ -9841,7 +10772,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115.2</v>
+        <v>116.2</v>
       </c>
     </row>
     <row r="11">
@@ -9881,7 +10812,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.15</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="15">
@@ -9891,7 +10822,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.25</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="16">
@@ -9901,7 +10832,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9399999999999999</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="17">
@@ -9911,7 +10842,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>51.64</v>
+        <v>46.54</v>
       </c>
     </row>
     <row r="18">
@@ -9921,7 +10852,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.3</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="19">
@@ -9931,7 +10862,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.21</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="20">
@@ -9941,7 +10872,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.26</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="21">
@@ -9951,7 +10882,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.87</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="22">
@@ -9961,7 +10892,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -9971,7 +10902,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -9981,7 +10912,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.45</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="25">
@@ -10001,7 +10932,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.85</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="27">
@@ -10021,7 +10952,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
